--- a/excel/ide_key.xlsx
+++ b/excel/ide_key.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mosby\Desktop\学习文件\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\Ai\小程序\Excel显示\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49B68162-C008-4A43-8537-50DF2E7D9E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8B92970-CF4A-4569-8A14-87502D11CDD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{BB3475BE-C968-477E-BFD9-25EAA248D3B5}"/>
   </bookViews>
   <sheets>
-    <sheet name="sheet0" sheetId="1" r:id="rId1"/>
+    <sheet name="VS Code&amp;Webstrom" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="103">
   <si>
     <t>序号</t>
   </si>
@@ -49,9 +49,6 @@
     <t>Ctrl+/</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>块注释</t>
   </si>
   <si>
@@ -61,9 +58,6 @@
     <t>Ctrl+Shift+/</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>重复选中</t>
   </si>
   <si>
@@ -73,9 +67,6 @@
     <t>Alt+J</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>多行同时编辑</t>
   </si>
   <si>
@@ -85,27 +76,18 @@
     <t>Shift+Alt+Insert</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>全局查找</t>
   </si>
   <si>
     <t>Ctrl+Shift+F</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>查找</t>
   </si>
   <si>
     <t>Ctrl+F</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>替换</t>
   </si>
   <si>
@@ -115,9 +97,6 @@
     <t>Ctrl+R</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
     <t>重命名文件/以及变量</t>
   </si>
   <si>
@@ -127,27 +106,18 @@
     <t>Shift+F6</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>查找下一个</t>
   </si>
   <si>
     <t>Enter/F3</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>查找上一个</t>
   </si>
   <si>
     <t>Shift+Enter/F3</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>上下行移动</t>
   </si>
   <si>
@@ -157,9 +127,6 @@
     <t>Shift+Alt+Up/Down</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>快速换行</t>
   </si>
   <si>
@@ -169,9 +136,6 @@
     <t>Shift+Enter</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
     <t>格式化代码</t>
   </si>
   <si>
@@ -181,9 +145,6 @@
     <t>Ctrl+Alt+L</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
     <t>关闭当前窗口</t>
   </si>
   <si>
@@ -193,9 +154,6 @@
     <t>Ctrl+F4</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>复制当前行</t>
   </si>
   <si>
@@ -205,9 +163,6 @@
     <t>Crtl+D</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
     <t>前进</t>
   </si>
   <si>
@@ -217,9 +172,6 @@
     <t>Ctrl+Alt+Right</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
     <t>后退</t>
   </si>
   <si>
@@ -229,9 +181,6 @@
     <t>Ctrl+Alt+Left</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
     <t>括号跳转</t>
   </si>
   <si>
@@ -241,9 +190,6 @@
     <t>Ctrl+Shift+M</t>
   </si>
   <si>
-    <t>19</t>
-  </si>
-  <si>
     <t>闭合代码</t>
   </si>
   <si>
@@ -253,9 +199,6 @@
     <t>CtrI+减号</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
     <t>展开代码</t>
   </si>
   <si>
@@ -265,9 +208,6 @@
     <t>Ctrl+加号</t>
   </si>
   <si>
-    <t>21</t>
-  </si>
-  <si>
     <t>展开所有代码</t>
   </si>
   <si>
@@ -277,9 +217,6 @@
     <t>Ctrl+Shift+加号</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
     <t>闭合所有代码</t>
   </si>
   <si>
@@ -289,9 +226,6 @@
     <t>Ctrl+Shift+减号</t>
   </si>
   <si>
-    <t>23</t>
-  </si>
-  <si>
     <t>格式化选中代码</t>
   </si>
   <si>
@@ -301,9 +235,6 @@
     <t>Ctrl+AIt+L</t>
   </si>
   <si>
-    <t>24</t>
-  </si>
-  <si>
     <t>多个光标</t>
   </si>
   <si>
@@ -313,9 +244,6 @@
     <t>Alt+左键</t>
   </si>
   <si>
-    <t>25</t>
-  </si>
-  <si>
     <t>删掉当前行代码</t>
   </si>
   <si>
@@ -325,27 +253,18 @@
     <t>Ctrl+Y</t>
   </si>
   <si>
-    <t>26</t>
-  </si>
-  <si>
     <t>大小写转换</t>
   </si>
   <si>
     <t>Ctrl+Shift+U</t>
   </si>
   <si>
-    <t>27</t>
-  </si>
-  <si>
     <t>终端</t>
   </si>
   <si>
     <t>Alt+F12</t>
   </si>
   <si>
-    <t>28</t>
-  </si>
-  <si>
     <t>查找引用</t>
   </si>
   <si>
@@ -355,42 +274,27 @@
     <t>Alt+F7</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
     <t>聚焦当前编辑文件</t>
   </si>
   <si>
     <t>Alt+F1,1</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>当前文件夹打开终端</t>
   </si>
   <si>
     <t>Alt+F1,0</t>
   </si>
   <si>
-    <t>31</t>
-  </si>
-  <si>
     <t>递进式选择代码块</t>
   </si>
   <si>
-    <t>32</t>
-  </si>
-  <si>
     <t>自动将下一行合并到当前行末尾</t>
   </si>
   <si>
     <t>Ctrl+ Shift+J</t>
   </si>
   <si>
-    <t>33</t>
-  </si>
-  <si>
     <t>打开文件</t>
   </si>
   <si>
@@ -400,27 +304,18 @@
     <t>Ctrl+ Shift +N</t>
   </si>
   <si>
-    <t>34</t>
-  </si>
-  <si>
     <t>显示最近复制内容</t>
   </si>
   <si>
     <t>Ctrl+ Shift+V</t>
   </si>
   <si>
-    <t>35</t>
-  </si>
-  <si>
     <t>自动结束代码，行末自动添加分号</t>
   </si>
   <si>
     <t>Ctrl+ Shift + Enter</t>
   </si>
   <si>
-    <t>36</t>
-  </si>
-  <si>
     <t>切换代码块顺序</t>
   </si>
   <si>
@@ -428,6 +323,24 @@
   </si>
   <si>
     <t>Ctrl+`</t>
+  </si>
+  <si>
+    <t>列1</t>
+  </si>
+  <si>
+    <t>求和</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>平均值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>汇总</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -435,7 +348,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -444,41 +357,19 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -486,41 +377,24 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -531,6 +405,18 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CF471C42-72EE-4727-B3A2-72D00ABAB20F}" name="表3" displayName="表3" ref="A1:D37" totalsRowShown="0">
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{EA927994-3D57-4431-AF4F-C6E686E9A83A}" name="序号" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{95565356-3792-41B0-AF09-2AD58EA18591}" name="描述"/>
+    <tableColumn id="3" xr3:uid="{D394F6F5-99FF-4DB4-915C-F0091C7A8648}" name="VS Code"/>
+    <tableColumn id="4" xr3:uid="{D1750771-1848-4FE2-8C21-2A735D238568}" name="Webstrom"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -829,537 +715,539 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EEA3857-A4E5-400C-A607-0CC102D5837F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E13F9F0-2007-4EBD-90B2-4CA254A26A37}">
   <dimension ref="A1:D37"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.9296875" customWidth="1"/>
-    <col min="2" max="2" width="31.46484375" customWidth="1"/>
-    <col min="3" max="4" width="20.59765625" customWidth="1"/>
+    <col min="1" max="1" width="5.86328125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="37.3984375" customWidth="1"/>
+    <col min="3" max="3" width="27.73046875" customWidth="1"/>
+    <col min="4" max="4" width="22.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+      <c r="C4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="D4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="3" t="s">
+    </row>
+    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="C5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
+      <c r="D5" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="1" t="s">
+    </row>
+    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C6" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
+      <c r="C7" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C8" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
+      <c r="B21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="B23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
+      <c r="B24" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B25" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" t="s">
+        <v>69</v>
+      </c>
+      <c r="D25" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="B26" t="s">
+        <v>71</v>
+      </c>
+      <c r="C26" t="s">
+        <v>72</v>
+      </c>
+      <c r="D26" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="B27" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="1">
         <v>27</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
+      <c r="B28" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28" t="s">
+        <v>97</v>
+      </c>
+      <c r="D28" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="1">
         <v>28</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B29" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29" t="s">
+        <v>79</v>
+      </c>
+      <c r="D29" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="B30" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="1">
         <v>30</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="B31" t="s">
+        <v>83</v>
+      </c>
+      <c r="C31" t="s">
+        <v>72</v>
+      </c>
+      <c r="D31" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="1">
         <v>31</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
+      <c r="B32" t="s">
+        <v>85</v>
+      </c>
+      <c r="C32" t="s">
+        <v>72</v>
+      </c>
+      <c r="D32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="1">
         <v>32</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B33" t="s">
+        <v>86</v>
+      </c>
+      <c r="C33" t="s">
+        <v>72</v>
+      </c>
+      <c r="D33" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="1">
         <v>33</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="B34" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" t="s">
+        <v>89</v>
+      </c>
+      <c r="D34" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="1">
         <v>34</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
+      <c r="B35" t="s">
+        <v>91</v>
+      </c>
+      <c r="C35" t="s">
+        <v>72</v>
+      </c>
+      <c r="D35" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="1">
         <v>35</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B36" t="s">
+        <v>93</v>
+      </c>
+      <c r="C36" t="s">
+        <v>72</v>
+      </c>
+      <c r="D36" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="1">
         <v>36</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="B37" t="s">
+        <v>95</v>
+      </c>
+      <c r="C37" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C26" s="3" t="s">
+      <c r="D37" t="s">
         <v>96</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>131</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-  <headerFooter alignWithMargins="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>